--- a/backend/wp_templates/J/J1 应付职工薪酬.xlsx
+++ b/backend/wp_templates/J/J1 应付职工薪酬.xlsx
@@ -31,10 +31,6 @@
     <sheet name="首发业务解答二-删除" sheetId="34" state="hidden" r:id="rId22"/>
     <sheet name="GT_Custom" sheetId="20" state="hidden" r:id="rId23"/>
   </sheets>
-  <externalReferences>
-    <externalReference r:id="rId24"/>
-    <externalReference r:id="rId25"/>
-  </externalReferences>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">'应付职工薪酬实质性程序表 J1A'!$A$16:$K$16</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2">'应付职工薪酬实质性程序表 J1A-原版'!$A$16:$P$139</definedName>
@@ -83,7 +79,6 @@
     <definedName name="XRefPaste3" localSheetId="2">#REF!</definedName>
     <definedName name="XRefPaste3Row" localSheetId="2">#REF!</definedName>
     <definedName name="本循环科目" localSheetId="2">#REF!</definedName>
-    <definedName name="本循环科目" localSheetId="3">[1]索引!$D$15:$D$76</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25867,359 +25862,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="索引"/>
-      <sheetName val="货币资金Cx"/>
-      <sheetName val="货币资金Mx"/>
-      <sheetName val="分录"/>
-      <sheetName val="标本-资产"/>
-      <sheetName val="企业表一"/>
-      <sheetName val="M-5C"/>
-      <sheetName val="M-5A"/>
-      <sheetName val="资产负债表"/>
-      <sheetName val="数量金额总账"/>
-      <sheetName val="设备部房屋"/>
-      <sheetName val="核算项目余额表"/>
-      <sheetName val="完"/>
-      <sheetName val="W"/>
-      <sheetName val="2004"/>
-      <sheetName val="B"/>
-      <sheetName val="表头"/>
-      <sheetName val="PER SALES ORG"/>
-      <sheetName val="1月"/>
-      <sheetName val="SW-TEO"/>
-      <sheetName val="Detailed Testing"/>
-      <sheetName val="银行借款询证"/>
-      <sheetName val="余额表"/>
-      <sheetName val="本期报表"/>
-      <sheetName val="breakdown"/>
-      <sheetName val="盈余公积 （合并)"/>
-      <sheetName val="Toolbox"/>
-      <sheetName val="eqpmad2"/>
-      <sheetName val="提足折旧"/>
-      <sheetName val="DATA"/>
-      <sheetName val="委托加工材料"/>
-      <sheetName val="材料采购-入库"/>
-      <sheetName val="原材料－其他"/>
-      <sheetName val="材料成本差异－运费等"/>
-      <sheetName val="邻酮定乙酚发出测试"/>
-      <sheetName val="管理费用(集团董事会)"/>
-      <sheetName val="Sheet1"/>
-      <sheetName val="FS"/>
-      <sheetName val="gl"/>
-      <sheetName val="Adm"/>
-      <sheetName val="sell"/>
-      <sheetName val="Fin"/>
-      <sheetName val="Erection"/>
-      <sheetName val="剥离前"/>
-      <sheetName val="XL4Poppy"/>
-      <sheetName val="08"/>
-      <sheetName val="02"/>
-      <sheetName val="03"/>
-      <sheetName val="04"/>
-      <sheetName val="05"/>
-      <sheetName val="06"/>
-      <sheetName val="07"/>
-      <sheetName val="10"/>
-      <sheetName val="09"/>
-      <sheetName val="UFPrn20031114182129"/>
-      <sheetName val="订单418"/>
-      <sheetName val="Collateral"/>
-      <sheetName val="Disposition"/>
-      <sheetName val="Validation"/>
-      <sheetName val="35.1租赁明细"/>
-      <sheetName val="中山低值"/>
-      <sheetName val="分产品销售收入、成本分析表"/>
-      <sheetName val="E1020"/>
-      <sheetName val="1月固定资产清单"/>
-      <sheetName val="关联方—创斯达"/>
-      <sheetName val="关联方—东风汽车"/>
-      <sheetName val="ZH1-4其他应收款个别认定"/>
-      <sheetName val="ZH1-3应收账款个别认定"/>
-      <sheetName val="各单位目标指标"/>
-      <sheetName val="新城资金明细"/>
-      <sheetName val="申鑫大厦租金明细"/>
-      <sheetName val="三林明细"/>
-      <sheetName val="东陆明细"/>
-      <sheetName val="4-货币资金-现金"/>
-      <sheetName val="基础信息"/>
-      <sheetName val="XREF"/>
-      <sheetName val="A430"/>
-      <sheetName val="货币资金审定表"/>
-      <sheetName val="balance"/>
-      <sheetName val="PRC-BS-SZ"/>
-      <sheetName val="A1"/>
-      <sheetName val="账面外销"/>
-      <sheetName val="销售费用Dy"/>
-      <sheetName val="细节测试审计抽样"/>
-      <sheetName val="YS02-02"/>
-      <sheetName val="短期借款Dy"/>
-      <sheetName val="采购订单3名"/>
-      <sheetName val="P12 TB SZ"/>
-      <sheetName val="选择报表"/>
-      <sheetName val="CF附注"/>
-      <sheetName val="试算平衡表"/>
-      <sheetName val="原TB表"/>
-      <sheetName val="工资"/>
-      <sheetName val="27-7"/>
-      <sheetName val="dxnsjtempsheet"/>
-      <sheetName val="５８D"/>
-      <sheetName val="存货明细表"/>
-      <sheetName val="清单12.31"/>
-      <sheetName val="短期投资股票投资.dbf"/>
-      <sheetName val="短期投资国债投资.dbf"/>
-      <sheetName val="股票投资收益.dbf"/>
-      <sheetName val="其他货币海通.dbf"/>
-      <sheetName val="其他货币零领路.dbf"/>
-      <sheetName val="投资收益债券.dbf"/>
-      <sheetName val="营业费用测试"/>
-      <sheetName val="科目余额表"/>
-      <sheetName val="凭证抽查表 "/>
-      <sheetName val="资产减值损失审核表"/>
-      <sheetName val="坯布"/>
-      <sheetName val="材料"/>
-      <sheetName val="外销"/>
-      <sheetName val="Summary"/>
-      <sheetName val="dghn"/>
-      <sheetName val="报表项目"/>
-      <sheetName val="01"/>
-      <sheetName val="010"/>
-      <sheetName val="011"/>
-      <sheetName val="012"/>
-      <sheetName val="表头（请先填写）"/>
-      <sheetName val="调整分录汇总表"/>
-      <sheetName val="明细表（账龄）D2-2"/>
-      <sheetName val="其他应付款科目余额2005.12.31"/>
-      <sheetName val="期末应付帐款明细表"/>
-      <sheetName val="期初应付帐款明细表"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0">
-        <row r="15">
-          <cell r="D15" t="str">
-            <v>货币资金</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="1" refreshError="1"/>
-      <sheetData sheetId="2" refreshError="1"/>
-      <sheetData sheetId="3" refreshError="1"/>
-      <sheetData sheetId="4" refreshError="1"/>
-      <sheetData sheetId="5" refreshError="1"/>
-      <sheetData sheetId="6" refreshError="1"/>
-      <sheetData sheetId="7" refreshError="1"/>
-      <sheetData sheetId="8" refreshError="1"/>
-      <sheetData sheetId="9" refreshError="1"/>
-      <sheetData sheetId="10" refreshError="1"/>
-      <sheetData sheetId="11" refreshError="1"/>
-      <sheetData sheetId="12" refreshError="1"/>
-      <sheetData sheetId="13" refreshError="1"/>
-      <sheetData sheetId="14" refreshError="1"/>
-      <sheetData sheetId="15" refreshError="1"/>
-      <sheetData sheetId="16" refreshError="1"/>
-      <sheetData sheetId="17" refreshError="1"/>
-      <sheetData sheetId="18" refreshError="1"/>
-      <sheetData sheetId="19" refreshError="1"/>
-      <sheetData sheetId="20" refreshError="1"/>
-      <sheetData sheetId="21" refreshError="1"/>
-      <sheetData sheetId="22" refreshError="1"/>
-      <sheetData sheetId="23" refreshError="1"/>
-      <sheetData sheetId="24" refreshError="1"/>
-      <sheetData sheetId="25" refreshError="1"/>
-      <sheetData sheetId="26" refreshError="1"/>
-      <sheetData sheetId="27" refreshError="1"/>
-      <sheetData sheetId="28" refreshError="1"/>
-      <sheetData sheetId="29" refreshError="1"/>
-      <sheetData sheetId="30" refreshError="1"/>
-      <sheetData sheetId="31" refreshError="1"/>
-      <sheetData sheetId="32" refreshError="1"/>
-      <sheetData sheetId="33" refreshError="1"/>
-      <sheetData sheetId="34" refreshError="1"/>
-      <sheetData sheetId="35" refreshError="1"/>
-      <sheetData sheetId="36" refreshError="1"/>
-      <sheetData sheetId="37" refreshError="1"/>
-      <sheetData sheetId="38" refreshError="1"/>
-      <sheetData sheetId="39" refreshError="1"/>
-      <sheetData sheetId="40" refreshError="1"/>
-      <sheetData sheetId="41" refreshError="1"/>
-      <sheetData sheetId="42" refreshError="1"/>
-      <sheetData sheetId="43" refreshError="1"/>
-      <sheetData sheetId="44" refreshError="1"/>
-      <sheetData sheetId="45" refreshError="1"/>
-      <sheetData sheetId="46" refreshError="1"/>
-      <sheetData sheetId="47" refreshError="1"/>
-      <sheetData sheetId="48" refreshError="1"/>
-      <sheetData sheetId="49" refreshError="1"/>
-      <sheetData sheetId="50" refreshError="1"/>
-      <sheetData sheetId="51" refreshError="1"/>
-      <sheetData sheetId="52" refreshError="1"/>
-      <sheetData sheetId="53" refreshError="1"/>
-      <sheetData sheetId="54" refreshError="1"/>
-      <sheetData sheetId="55" refreshError="1"/>
-      <sheetData sheetId="56" refreshError="1"/>
-      <sheetData sheetId="57" refreshError="1"/>
-      <sheetData sheetId="58" refreshError="1"/>
-      <sheetData sheetId="59" refreshError="1"/>
-      <sheetData sheetId="60" refreshError="1"/>
-      <sheetData sheetId="61" refreshError="1"/>
-      <sheetData sheetId="62" refreshError="1"/>
-      <sheetData sheetId="63" refreshError="1"/>
-      <sheetData sheetId="64" refreshError="1"/>
-      <sheetData sheetId="65" refreshError="1"/>
-      <sheetData sheetId="66" refreshError="1"/>
-      <sheetData sheetId="67" refreshError="1"/>
-      <sheetData sheetId="68" refreshError="1"/>
-      <sheetData sheetId="69" refreshError="1"/>
-      <sheetData sheetId="70" refreshError="1"/>
-      <sheetData sheetId="71" refreshError="1"/>
-      <sheetData sheetId="72" refreshError="1"/>
-      <sheetData sheetId="73" refreshError="1"/>
-      <sheetData sheetId="74" refreshError="1"/>
-      <sheetData sheetId="75" refreshError="1"/>
-      <sheetData sheetId="76" refreshError="1"/>
-      <sheetData sheetId="77" refreshError="1"/>
-      <sheetData sheetId="78" refreshError="1"/>
-      <sheetData sheetId="79" refreshError="1"/>
-      <sheetData sheetId="80" refreshError="1"/>
-      <sheetData sheetId="81" refreshError="1"/>
-      <sheetData sheetId="82" refreshError="1"/>
-      <sheetData sheetId="83" refreshError="1"/>
-      <sheetData sheetId="84" refreshError="1"/>
-      <sheetData sheetId="85" refreshError="1"/>
-      <sheetData sheetId="86" refreshError="1"/>
-      <sheetData sheetId="87" refreshError="1"/>
-      <sheetData sheetId="88" refreshError="1"/>
-      <sheetData sheetId="89" refreshError="1"/>
-      <sheetData sheetId="90" refreshError="1"/>
-      <sheetData sheetId="91" refreshError="1"/>
-      <sheetData sheetId="92" refreshError="1"/>
-      <sheetData sheetId="93" refreshError="1"/>
-      <sheetData sheetId="94" refreshError="1"/>
-      <sheetData sheetId="95" refreshError="1"/>
-      <sheetData sheetId="96" refreshError="1"/>
-      <sheetData sheetId="97" refreshError="1"/>
-      <sheetData sheetId="98" refreshError="1"/>
-      <sheetData sheetId="99" refreshError="1"/>
-      <sheetData sheetId="100" refreshError="1"/>
-      <sheetData sheetId="101" refreshError="1"/>
-      <sheetData sheetId="102" refreshError="1"/>
-      <sheetData sheetId="103" refreshError="1"/>
-      <sheetData sheetId="104" refreshError="1"/>
-      <sheetData sheetId="105" refreshError="1"/>
-      <sheetData sheetId="106" refreshError="1"/>
-      <sheetData sheetId="107" refreshError="1"/>
-      <sheetData sheetId="108" refreshError="1"/>
-      <sheetData sheetId="109" refreshError="1"/>
-      <sheetData sheetId="110" refreshError="1"/>
-      <sheetData sheetId="111" refreshError="1"/>
-      <sheetData sheetId="112" refreshError="1"/>
-      <sheetData sheetId="113" refreshError="1"/>
-      <sheetData sheetId="114" refreshError="1"/>
-      <sheetData sheetId="115" refreshError="1"/>
-      <sheetData sheetId="116" refreshError="1"/>
-      <sheetData sheetId="117" refreshError="1"/>
-      <sheetData sheetId="118" refreshError="1"/>
-      <sheetData sheetId="119" refreshError="1"/>
-      <sheetData sheetId="120" refreshError="1"/>
-      <sheetData sheetId="121" refreshError="1"/>
-      <sheetData sheetId="122" refreshError="1"/>
-      <sheetData sheetId="123" refreshError="1"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
-<file path=xl/externalLinks/externalLink2.xml><?xml version="1.0" encoding="utf-8"?>
-<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
-  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
-    <sheetNames>
-      <sheetName val="IPO企业薪酬审计提示"/>
-      <sheetName val="IPO企业股权激励工具关注的审计重点"/>
-      <sheetName val="首发业务解答二"/>
-      <sheetName val="底稿目录"/>
-      <sheetName val="应付职工薪酬实质性程序表 L1A"/>
-      <sheetName val="审定表L1 "/>
-      <sheetName val="附注披露信息（上市公司）L1-1"/>
-      <sheetName val="附注披露信息L1-1（国有企业）"/>
-      <sheetName val="明细表L1-2 "/>
-      <sheetName val="调整分录汇总表L1-2-1"/>
-      <sheetName val="分析表L1-3-1"/>
-      <sheetName val="分析表L1-3-2"/>
-      <sheetName val="计提情况检查表L1-4-1"/>
-      <sheetName val="分配情况检查表L1-4-2"/>
-      <sheetName val="非货币性福利检查表L1-4-3"/>
-      <sheetName val="辞退福利检查表L1-4-4"/>
-      <sheetName val="股份支付检查表L1-4-5"/>
-      <sheetName val="应付职工薪酬余额及期后事项检查表L1-4-6"/>
-      <sheetName val="职工薪酬政策统计表L1-4-7"/>
-      <sheetName val="细节测试表L1-5"/>
-      <sheetName val="带薪缺勤L1-8"/>
-      <sheetName val="股份支付L1-9"/>
-      <sheetName val="GT_Custom"/>
-    </sheetNames>
-    <sheetDataSet>
-      <sheetData sheetId="0"/>
-      <sheetData sheetId="1"/>
-      <sheetData sheetId="2"/>
-      <sheetData sheetId="3">
-        <row r="2">
-          <cell r="A2" t="str">
-            <v>客户名称：</v>
-          </cell>
-        </row>
-        <row r="3">
-          <cell r="A3" t="str">
-            <v>截止日：2022年12月31日</v>
-          </cell>
-        </row>
-        <row r="4">
-          <cell r="A4" t="str">
-            <v>编制人：</v>
-          </cell>
-        </row>
-        <row r="5">
-          <cell r="A5" t="str">
-            <v>编制日期：</v>
-          </cell>
-        </row>
-        <row r="6">
-          <cell r="A6" t="str">
-            <v>复核人：</v>
-          </cell>
-        </row>
-        <row r="7">
-          <cell r="A7" t="str">
-            <v>复核日期：</v>
-          </cell>
-        </row>
-      </sheetData>
-      <sheetData sheetId="4"/>
-      <sheetData sheetId="5"/>
-      <sheetData sheetId="6"/>
-      <sheetData sheetId="7"/>
-      <sheetData sheetId="8"/>
-      <sheetData sheetId="9"/>
-      <sheetData sheetId="10"/>
-      <sheetData sheetId="11"/>
-      <sheetData sheetId="12"/>
-      <sheetData sheetId="13"/>
-      <sheetData sheetId="14"/>
-      <sheetData sheetId="15"/>
-      <sheetData sheetId="16"/>
-      <sheetData sheetId="17"/>
-      <sheetData sheetId="18"/>
-      <sheetData sheetId="19"/>
-      <sheetData sheetId="20"/>
-      <sheetData sheetId="21"/>
-      <sheetData sheetId="22"/>
-    </sheetDataSet>
-  </externalBook>
-</externalLink>
-</file>
-
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 主题​​">
   <a:themeElements>
@@ -42905,17 +42547,14 @@
     </row>
     <row r="3" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A3" s="353" t="str">
-        <f>[2]底稿目录!A2</f>
         <v>客户名称：</v>
       </c>
       <c r="B3" s="353"/>
       <c r="C3" s="144" t="str">
-        <f>[2]底稿目录!A4</f>
         <v>编制人：</v>
       </c>
       <c r="D3" s="353"/>
       <c r="E3" s="354" t="str">
-        <f>[2]底稿目录!A5</f>
         <v>编制日期：</v>
       </c>
       <c r="F3" s="354"/>
@@ -42932,17 +42571,14 @@
     </row>
     <row r="4" spans="1:15" ht="20.100000000000001" customHeight="1">
       <c r="A4" s="356" t="str">
-        <f>[2]底稿目录!A3</f>
         <v>截止日：2022年12月31日</v>
       </c>
       <c r="B4" s="353"/>
       <c r="C4" s="149" t="str">
-        <f>[2]底稿目录!A6</f>
         <v>复核人：</v>
       </c>
       <c r="D4" s="353"/>
       <c r="E4" s="354" t="str">
-        <f>[2]底稿目录!A7</f>
         <v>复核日期：</v>
       </c>
       <c r="F4" s="354"/>
